--- a/Trans To Vostok/Korean/Texture.xlsx
+++ b/Trans To Vostok/Korean/Texture.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SteamLibrary\steamapps\common\Road to Vostok\mods\Trans To Vostok\Trans To Vostok\Korean\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A80801F4-D229-437A-BE2B-D75E4D4E143D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38A0491F-EBBB-4921-87F4-D40C67D9271C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" activeTab="1" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" xr2:uid="{E0CAA4CC-5EC0-4298-9780-F39DB2CE6684}"/>
   </bookViews>
   <sheets>
     <sheet name="Tutorial" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="91">
   <si>
     <t>Tutorial</t>
   </si>
@@ -621,9 +621,6 @@
   </si>
   <si>
     <t>MuteJack</t>
-  </si>
-  <si>
-    <t>MuteJack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -663,6 +660,10 @@
 Crumpled Paper: Pixabay (https://pixabay.com/ko/photos/%ea%b5%ac%ea%b2%a8%ec%a7%84-%ec%a2%85%ec%9d%b4-%eb%b8%94%eb%9e%99-%ec%a2%85%ec%9d%b4-6793287/)
 Airplane Icon: Pixabay (https://pixabay.com/vectors/airplane-)transportation-symbol-icon-23997/
 Masking Tape: Texturelabs (https://texturelabs.org/textures/details_122/)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Contributors</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1120,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88310B32-1EF1-4265-A60F-0339C38439EB}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="2" width="8.796875" style="2"/>
@@ -1129,11 +1130,11 @@
     <col min="5" max="5" width="66.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="58.296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="69.296875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.3984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="53.19921875" style="5" customWidth="1"/>
+    <col min="8" max="9" width="14.3984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.19921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
@@ -1141,28 +1142,31 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="261">
+      <c r="I1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="261">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -1187,11 +1191,11 @@
       <c r="H2" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="I2" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="208.8">
+      <c r="J2" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="208.8">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -1214,10 +1218,10 @@
         <v>12</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="261">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1240,10 +1244,10 @@
         <v>43</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="243.6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="243.6">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -1266,10 +1270,10 @@
         <v>42</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="261">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
@@ -1292,10 +1296,10 @@
         <v>44</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="278.39999999999998">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="278.39999999999998">
       <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
@@ -1318,10 +1322,10 @@
         <v>45</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="313.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="313.2">
       <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
@@ -1344,10 +1348,10 @@
         <v>46</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="261">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -1370,10 +1374,10 @@
         <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="261">
       <c r="A10" s="1" t="s">
         <v>1</v>
       </c>
@@ -1396,10 +1400,10 @@
         <v>48</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="400.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="400.2">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -1422,10 +1426,10 @@
         <v>49</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="261">
       <c r="A12" s="1" t="s">
         <v>1</v>
       </c>
@@ -1448,10 +1452,10 @@
         <v>50</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="261">
       <c r="A13" s="1" t="s">
         <v>1</v>
       </c>
@@ -1474,10 +1478,10 @@
         <v>13</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="261">
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
@@ -1500,10 +1504,10 @@
         <v>51</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="278.39999999999998">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="278.39999999999998">
       <c r="A15" s="2" t="s">
         <v>0</v>
       </c>
@@ -1526,10 +1530,10 @@
         <v>52</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="243.6">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="243.6">
       <c r="A16" s="2" t="s">
         <v>0</v>
       </c>
@@ -1552,10 +1556,10 @@
         <v>53</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="261">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="261">
       <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
@@ -1578,10 +1582,10 @@
         <v>54</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="I17" s="5" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1592,7 +1596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61281094-5A26-43DB-B173-C8F47C01DA95}">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999"/>
   <cols>
     <col min="1" max="2" width="8.796875" style="2"/>
@@ -1601,11 +1605,11 @@
     <col min="5" max="5" width="66.5" style="2" customWidth="1"/>
     <col min="6" max="6" width="58.296875" style="2" customWidth="1"/>
     <col min="7" max="7" width="69.296875" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.3984375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="53.19921875" style="5" customWidth="1"/>
+    <col min="8" max="9" width="14.3984375" style="2" customWidth="1"/>
+    <col min="10" max="10" width="53.19921875" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" s="7" t="s">
         <v>6</v>
       </c>
@@ -1613,28 +1617,31 @@
         <v>7</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="I1" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="174">
+      <c r="I1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="174">
       <c r="A2" s="1" t="s">
         <v>73</v>
       </c>
@@ -1657,13 +1664,13 @@
         <v>77</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>80</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -1672,7 +1679,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1681,7 +1688,7 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:10">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1690,7 +1697,7 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1699,7 +1706,7 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1708,7 +1715,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1717,7 +1724,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1726,7 +1733,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:10">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1735,7 +1742,7 @@
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:10">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1744,7 +1751,7 @@
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:10">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1753,7 +1760,7 @@
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:10">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1762,17 +1769,17 @@
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:10">
       <c r="D14" s="4"/>
       <c r="E14" s="5"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:10">
       <c r="D15" s="4"/>
       <c r="E15" s="5"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:10">
       <c r="C16" s="1"/>
       <c r="D16" s="4"/>
       <c r="E16" s="5"/>
